--- a/VerveStacks_GHA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_GHA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB8B6E65-B005-4533-954C-4B3702B45F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B1A361B-5ABF-4A07-AD85-879E46B7F3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C915FE29-4D43-4BB7-9586-CED10724EE23}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4DDAC40E-33E9-4862-A70F-E6324CCD1293}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -520,7 +520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06213116-D091-4297-94EE-55DC0F78C9ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6098D38D-57E4-4393-BFD3-C6A7E99C5C15}">
   <dimension ref="B3:L11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_GHA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_GHA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B1A361B-5ABF-4A07-AD85-879E46B7F3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BB1DB89-B086-4C20-AD04-6C429ED1EAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4DDAC40E-33E9-4862-A70F-E6324CCD1293}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1F439F9F-E762-447F-AD7E-96E485F84657}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -520,7 +520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6098D38D-57E4-4393-BFD3-C6A7E99C5C15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBCE5CE7-AC04-4A30-924A-69F2DA54FA0A}">
   <dimension ref="B3:L11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
